--- a/Colocalization/coloc.xlsx
+++ b/Colocalization/coloc.xlsx
@@ -112,19 +112,19 @@
         <v>104.0</v>
       </c>
       <c r="C2" t="n">
-        <v>2.8490511236798906E-106</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1.9765274376249147E-4</v>
-      </c>
-      <c r="E2" t="n">
-        <v>5.212706009672331E-105</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.0026191283195807482</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.997183218936654</v>
+        <v>2.849050760758252E-106</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.9765274375921078E-4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5.212705345660446E-105</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.002619128319520675</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.9971832189367107</v>
       </c>
     </row>
   </sheetData>
@@ -220,19 +220,19 @@
         <v>101.0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.05120623951560035</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.9371120438344251</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1.766385762235179E-4</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.003224335805064254</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.008280742268686499</v>
+        <v>0.05120633081886231</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.9371137147516265</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.7654709960532062E-4</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.003222661711966314</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.008280745617939515</v>
       </c>
     </row>
   </sheetData>

--- a/Colocalization/coloc.xlsx
+++ b/Colocalization/coloc.xlsx
@@ -382,19 +382,19 @@
         <v>105.0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.05174277079866774</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.9467188599036195</v>
-      </c>
-      <c r="E2" t="n">
-        <v>6.146480875542043E-6</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1.1103876498246292E-4</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.001421184051854876</v>
+        <v>0.05174276372683873</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.9467187305129086</v>
+      </c>
+      <c r="E2" t="n">
+        <v>6.153540370894893E-6</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.1116792979064372E-4</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.0014211842900909684</v>
       </c>
     </row>
   </sheetData>
@@ -436,19 +436,19 @@
         <v>85.0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.051317465992539266</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.9401089595345832</v>
-      </c>
-      <c r="E2" t="n">
-        <v>9.259042004574929E-5</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.001689416180669716</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.0067915678721619886</v>
+        <v>0.05131751015325636</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.940109768535671</v>
+      </c>
+      <c r="E2" t="n">
+        <v>9.254609223662711E-5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.001688604115312793</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.006791571103523555</v>
       </c>
     </row>
   </sheetData>

--- a/Colocalization/coloc.xlsx
+++ b/Colocalization/coloc.xlsx
@@ -6,18 +6,19 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="HF" r:id="rId3" sheetId="1"/>
-    <sheet name="CAD" r:id="rId4" sheetId="2"/>
-    <sheet name="MI" r:id="rId5" sheetId="3"/>
-    <sheet name="IS" r:id="rId6" sheetId="4"/>
-    <sheet name="Hypertension" r:id="rId7" sheetId="5"/>
-    <sheet name="T2DM" r:id="rId8" sheetId="6"/>
+    <sheet name="eBMD" r:id="rId3" sheetId="1"/>
+    <sheet name="HF" r:id="rId4" sheetId="2"/>
+    <sheet name="CAD" r:id="rId5" sheetId="3"/>
+    <sheet name="MI" r:id="rId6" sheetId="4"/>
+    <sheet name="IS" r:id="rId7" sheetId="5"/>
+    <sheet name="Hypertension" r:id="rId8" sheetId="6"/>
+    <sheet name="T2DM" r:id="rId9" sheetId="7"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="6">
   <si>
     <t>nsnps</t>
   </si>
@@ -108,6 +109,60 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
+        <v>104.0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2.849050760758252E-106</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.9765274375921078E-4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5.212705345660446E-105</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.002619128319520675</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.9971832189367107</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
         <v>105.0</v>
       </c>
       <c r="C2" t="n">
@@ -131,7 +186,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -165,27 +220,27 @@
         <v>101.0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.05120633081886231</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.9371137147516265</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1.7654709960532062E-4</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.003222661711966314</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.008280745617939515</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+        <v>0.05120623951560035</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.9371120438344251</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.766385762235179E-4</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.003224335805064254</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.008280742268686499</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -239,7 +294,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -293,7 +348,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -327,73 +382,73 @@
         <v>105.0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.05174277079866774</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.9467188599036195</v>
-      </c>
-      <c r="E2" t="n">
-        <v>6.146480875542043E-6</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1.1103876498246292E-4</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.001421184051854876</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1"/>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="n">
-        <v>85.0</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.05131751015325636</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.940109768535671</v>
-      </c>
-      <c r="E2" t="n">
-        <v>9.254609223662711E-5</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.001688604115312793</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.006791571103523555</v>
+        <v>0.05174276372683873</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.9467187305129086</v>
+      </c>
+      <c r="E2" t="n">
+        <v>6.153540370894893E-6</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.1116792979064372E-4</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.0014211842900909684</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>102.0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.04940234772677003</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.9036648232551706</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0019059141042463781</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.034852693869333026</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.010174221044479861</v>
       </c>
     </row>
   </sheetData>
